--- a/人员数据导入模板.xlsx
+++ b/人员数据导入模板.xlsx
@@ -2,46 +2,216 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="11520" windowHeight="13380" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人员数据导入" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="26">
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FFCC0000"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <i val="1"/>
-      <color rgb="00808080"/>
+      <color rgb="FF808080"/>
       <sz val="9"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color indexed="8"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
-      <color rgb="00CC0000"/>
-      <sz val="10"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill/>
     </fill>
@@ -50,18 +220,204 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FF4472C4"/>
+        <bgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -70,27 +426,338 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -443,7 +1110,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -453,15 +1119,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F32"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="24.4444444444444" customWidth="1" min="1" max="1"/>
+    <col width="10.1111111111111" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="15.9722222222222" customWidth="1" min="4" max="4"/>
+    <col width="22.2222222222222" customWidth="1" min="5" max="5"/>
+    <col width="19.3796296296296" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -509,11 +1175,7 @@
       <c r="F2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>如 zhangsan，用于登录</t>
-        </is>
-      </c>
+      <c r="A3" s="4" t="n"/>
       <c r="B3" s="4" t="inlineStr">
         <is>
           <t>如 张三</t>
@@ -541,98 +1203,872 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>lisi</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>13800138001</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>123456</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>T3GTC</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>普通员工</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>luoyongzhen</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>骆勇贞</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>13437801897</v>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>T3GTC</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>管理员</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>wangwu</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>13800138002</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>123456</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>东区</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>huguang</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>胡光</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>13710920570</v>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>T3GTC</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>普通员工</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>zhaoliu</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>赵六</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>13800138003</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>654321</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>公共区</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>qiuwenxi</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>邱文希</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>13502241235</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>T3GTC</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>普通员工</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>hongjianming</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>洪建明</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>15814822224</v>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>T3GTC</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>管理员</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>linyanhua</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>林燕华</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>13539791289</v>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>T3GTC</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>普通员工</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>chenmingyuan</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>陈明远</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>13149366640</v>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>T3GTC</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>普通员工</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>kuangyuwei</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>邝禹玮</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>17708400392</v>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>T3GTC</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>普通员工</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>lijianhao</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>李键豪</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>13725342067</v>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>T3GTC</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>普通员工</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>wenyongxiong</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>温永雄</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>15099939861</v>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>T3GTC</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>普通员工</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>yangjinwei</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>杨锦炜</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>18202030173</v>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>T3GTC</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>普通员工</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>lanxinghuan</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>蓝兴焕</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>13553937981</v>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>T3GTC</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>普通员工</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>liangzijian</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>梁梓健</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>19927414927</v>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>T3GTC</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>普通员工</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>liguorong</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>李国荣</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>13535175078</v>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>T3GTC</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>普通员工</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>liaoliang</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>廖亮</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>13326960519</v>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>T3GTC</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>普通员工</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>wuyitong</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>吴艺通</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>15814881405</v>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>T3GTC</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>leixiang</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>雷湘</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>19176436601</v>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>T3GTC</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>普通员工</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>lijize</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>李继泽</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>18218617721</v>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>T3GTC</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>普通员工</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>zhubohong</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>朱博鸿</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>18819137891</v>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>T3GTC</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>liyongfa</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>李永发</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>15818180245</v>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>T3GTC</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>普通员工</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>yeyuanqing</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>叶远青</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>13611461242</v>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>T3GTC</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>普通员工</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>lujunlin</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>卢俊林</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>15697752887</v>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>T3GTC</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>普通员工</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>chenzhibing</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>陈志兵</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>13544348586</v>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>T3GTC</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>普通员工</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>zhijiewen</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>植杰文</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>13265034010</v>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>T3GTC</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>普通员工</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>xuanzhihao</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>禤志浩</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>13539778821</v>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>T3GTC</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>weishengfeng</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>魏胜峰</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>14749289767</v>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>T3GTC</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>普通员工</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>fangzhenzhen</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>方震震</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>15919301758</v>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>T3GTC</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>普通员工</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>peipengfei</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>裴鹏飞</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>13570261126</v>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>T3GTC</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>普通员工</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>dengyongchao</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>邓勇超</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>13697425621</v>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>T3GTC</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>普通员工</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>xiezeyi</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>谢泽仪</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>13711689996</v>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>T3GTC</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>普通员工</t>
         </is>
       </c>
     </row>
